--- a/nr-release/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-release/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T12:54:15+00:00</t>
+    <t>2026-02-18T12:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-release/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-release/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T12:55:13+00:00</t>
+    <t>2026-02-18T13:24:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-release/ig/StructureDefinition-mesures-diagnostic-report.xlsx
+++ b/nr-release/ig/StructureDefinition-mesures-diagnostic-report.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T13:24:18+00:00</t>
+    <t>2026-02-18T13:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
